--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08T06:48:03+00:00</t>
+          <t>2026-10-09T06:56:09+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4235</v>
+        <v>4236</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T06:48:03+00:00</t>
+          <t>2026-10-09T06:56:09+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4235</v>
+        <v>4236</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-08T06:48:03+00:00</t>
+          <t>2026-10-09T06:56:09+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4237</v>
+        <v>4238</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4236"/>
+  <dimension ref="A1:B4237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34463,6 +34463,14 @@
       </c>
       <c r="B4236" t="n">
         <v>14510</v>
+      </c>
+    </row>
+    <row r="4237">
+      <c r="A4237" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B4237" t="n">
+        <v>14526</v>
       </c>
     </row>
   </sheetData>
@@ -34476,7 +34484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4236"/>
+  <dimension ref="A1:B4237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68369,6 +68377,14 @@
       </c>
       <c r="B4236" t="n">
         <v>14422</v>
+      </c>
+    </row>
+    <row r="4237">
+      <c r="A4237" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B4237" t="n">
+        <v>14417</v>
       </c>
     </row>
   </sheetData>
@@ -68382,7 +68398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4238"/>
+  <dimension ref="A1:B4239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102293,6 +102309,14 @@
         <v>239875</v>
       </c>
     </row>
+    <row r="4239">
+      <c r="A4239" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B4239" t="n">
+        <v>235225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-09T06:56:09+00:00</t>
+          <t>2026-10-09T15:29:42+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-09T06:56:09+00:00</t>
+          <t>2026-10-09T15:29:42+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-09T06:56:09+00:00</t>
+          <t>2026-10-09T15:29:42+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-09T15:29:42+00:00</t>
+          <t>2026-10-12T06:43:31+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4236</v>
+        <v>4237</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-09T15:29:42+00:00</t>
+          <t>2026-10-12T06:43:31+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4236</v>
+        <v>4237</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-09T15:29:42+00:00</t>
+          <t>2026-10-12T06:43:31+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4238</v>
+        <v>4239</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4237"/>
+  <dimension ref="A1:B4238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34471,6 +34471,14 @@
       </c>
       <c r="B4237" t="n">
         <v>14526</v>
+      </c>
+    </row>
+    <row r="4238">
+      <c r="A4238" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4238" t="n">
+        <v>14689</v>
       </c>
     </row>
   </sheetData>
@@ -34484,7 +34492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4237"/>
+  <dimension ref="A1:B4238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68385,6 +68393,14 @@
       </c>
       <c r="B4237" t="n">
         <v>14417</v>
+      </c>
+    </row>
+    <row r="4238">
+      <c r="A4238" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4238" t="n">
+        <v>14570</v>
       </c>
     </row>
   </sheetData>
@@ -68398,7 +68414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4239"/>
+  <dimension ref="A1:B4240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102317,6 +102333,14 @@
         <v>235225</v>
       </c>
     </row>
+    <row r="4240">
+      <c r="A4240" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4240" t="n">
+        <v>233025</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-12T06:43:31+00:00</t>
+          <t>2026-10-13T07:13:59+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4237</v>
+        <v>4238</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-12T06:43:31+00:00</t>
+          <t>2026-10-13T07:13:59+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4237</v>
+        <v>4238</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-12T06:43:31+00:00</t>
+          <t>2026-10-13T07:13:59+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4239</v>
+        <v>4240</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4238"/>
+  <dimension ref="A1:B4239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34479,6 +34479,14 @@
       </c>
       <c r="B4238" t="n">
         <v>14689</v>
+      </c>
+    </row>
+    <row r="4239">
+      <c r="A4239" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B4239" t="n">
+        <v>14822</v>
       </c>
     </row>
   </sheetData>
@@ -34492,7 +34500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4238"/>
+  <dimension ref="A1:B4239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68401,6 +68409,14 @@
       </c>
       <c r="B4238" t="n">
         <v>14570</v>
+      </c>
+    </row>
+    <row r="4239">
+      <c r="A4239" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B4239" t="n">
+        <v>14657.5</v>
       </c>
     </row>
   </sheetData>
@@ -68414,7 +68430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4240"/>
+  <dimension ref="A1:B4241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102341,6 +102357,14 @@
         <v>233025</v>
       </c>
     </row>
+    <row r="4241">
+      <c r="A4241" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B4241" t="n">
+        <v>231275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:13:59+00:00</t>
+          <t>2026-10-14T05:37:11+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4238</v>
+        <v>4239</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-13T07:13:59+00:00</t>
+          <t>2026-10-14T05:37:11+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4238</v>
+        <v>4239</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-13T07:13:59+00:00</t>
+          <t>2026-10-14T05:37:11+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4240</v>
+        <v>4241</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4239"/>
+  <dimension ref="A1:B4240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34487,6 +34487,14 @@
       </c>
       <c r="B4239" t="n">
         <v>14822</v>
+      </c>
+    </row>
+    <row r="4240">
+      <c r="A4240" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4240" t="n">
+        <v>14741</v>
       </c>
     </row>
   </sheetData>
@@ -34500,7 +34508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4239"/>
+  <dimension ref="A1:B4240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68417,6 +68425,14 @@
       </c>
       <c r="B4239" t="n">
         <v>14657.5</v>
+      </c>
+    </row>
+    <row r="4240">
+      <c r="A4240" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4240" t="n">
+        <v>14625.5</v>
       </c>
     </row>
   </sheetData>
@@ -68430,7 +68446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4241"/>
+  <dimension ref="A1:B4242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102365,6 +102381,14 @@
         <v>231275</v>
       </c>
     </row>
+    <row r="4242">
+      <c r="A4242" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4242" t="n">
+        <v>229650</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-14T05:37:11+00:00</t>
+          <t>2026-10-15T05:24:42+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4239</v>
+        <v>4240</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-14T05:37:11+00:00</t>
+          <t>2026-10-15T05:24:42+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4239</v>
+        <v>4240</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-14T05:37:11+00:00</t>
+          <t>2026-10-15T05:24:42+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4241</v>
+        <v>4242</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4240"/>
+  <dimension ref="A1:B4241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34495,6 +34495,14 @@
       </c>
       <c r="B4240" t="n">
         <v>14741</v>
+      </c>
+    </row>
+    <row r="4241">
+      <c r="A4241" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4241" t="n">
+        <v>14751</v>
       </c>
     </row>
   </sheetData>
@@ -34508,7 +34516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4240"/>
+  <dimension ref="A1:B4241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68433,6 +68441,14 @@
       </c>
       <c r="B4240" t="n">
         <v>14625.5</v>
+      </c>
+    </row>
+    <row r="4241">
+      <c r="A4241" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4241" t="n">
+        <v>14635</v>
       </c>
     </row>
   </sheetData>
@@ -68446,7 +68462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4242"/>
+  <dimension ref="A1:B4243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102389,6 +102405,14 @@
         <v>229650</v>
       </c>
     </row>
+    <row r="4243">
+      <c r="A4243" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4243" t="n">
+        <v>228000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-15T05:24:42+00:00</t>
+          <t>2026-10-16T05:16:56+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4240</v>
+        <v>4241</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-15T05:24:42+00:00</t>
+          <t>2026-10-16T05:16:56+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4240</v>
+        <v>4241</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-15T05:24:42+00:00</t>
+          <t>2026-10-16T05:16:56+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4242</v>
+        <v>4243</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4241"/>
+  <dimension ref="A1:B4242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34503,6 +34503,14 @@
       </c>
       <c r="B4241" t="n">
         <v>14751</v>
+      </c>
+    </row>
+    <row r="4242">
+      <c r="A4242" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4242" t="n">
+        <v>14539</v>
       </c>
     </row>
   </sheetData>
@@ -34516,7 +34524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4241"/>
+  <dimension ref="A1:B4242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68449,6 +68457,14 @@
       </c>
       <c r="B4241" t="n">
         <v>14635</v>
+      </c>
+    </row>
+    <row r="4242">
+      <c r="A4242" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4242" t="n">
+        <v>14362</v>
       </c>
     </row>
   </sheetData>
@@ -68462,7 +68478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4243"/>
+  <dimension ref="A1:B4244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102413,6 +102429,14 @@
         <v>228000</v>
       </c>
     </row>
+    <row r="4244">
+      <c r="A4244" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4244" t="n">
+        <v>226600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-16T05:16:56+00:00</t>
+          <t>2026-10-19T05:28:53+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4241</v>
+        <v>4242</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-16T05:16:56+00:00</t>
+          <t>2026-10-19T05:28:53+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4241</v>
+        <v>4242</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-16T05:16:56+00:00</t>
+          <t>2026-10-19T05:28:53+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4243</v>
+        <v>4244</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4242"/>
+  <dimension ref="A1:B4243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34511,6 +34511,14 @@
       </c>
       <c r="B4242" t="n">
         <v>14539</v>
+      </c>
+    </row>
+    <row r="4243">
+      <c r="A4243" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4243" t="n">
+        <v>14595</v>
       </c>
     </row>
   </sheetData>
@@ -34524,7 +34532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4242"/>
+  <dimension ref="A1:B4243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68465,6 +68473,14 @@
       </c>
       <c r="B4242" t="n">
         <v>14362</v>
+      </c>
+    </row>
+    <row r="4243">
+      <c r="A4243" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4243" t="n">
+        <v>14485</v>
       </c>
     </row>
   </sheetData>
@@ -68478,7 +68494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4244"/>
+  <dimension ref="A1:B4245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102437,6 +102453,14 @@
         <v>226600</v>
       </c>
     </row>
+    <row r="4245">
+      <c r="A4245" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4245" t="n">
+        <v>225425</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-19T05:28:53+00:00</t>
+          <t>2026-10-20T05:30:48+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4242</v>
+        <v>4243</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-19T05:28:53+00:00</t>
+          <t>2026-10-20T05:30:48+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4242</v>
+        <v>4243</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-19T05:28:53+00:00</t>
+          <t>2026-10-20T05:30:48+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4244</v>
+        <v>4245</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4243"/>
+  <dimension ref="A1:B4244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34519,6 +34519,14 @@
       </c>
       <c r="B4243" t="n">
         <v>14595</v>
+      </c>
+    </row>
+    <row r="4244">
+      <c r="A4244" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4244" t="n">
+        <v>14496</v>
       </c>
     </row>
   </sheetData>
@@ -34532,7 +34540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4243"/>
+  <dimension ref="A1:B4244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68481,6 +68489,14 @@
       </c>
       <c r="B4243" t="n">
         <v>14485</v>
+      </c>
+    </row>
+    <row r="4244">
+      <c r="A4244" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4244" t="n">
+        <v>14378</v>
       </c>
     </row>
   </sheetData>
@@ -68494,7 +68510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4245"/>
+  <dimension ref="A1:B4246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102461,6 +102477,14 @@
         <v>225425</v>
       </c>
     </row>
+    <row r="4246">
+      <c r="A4246" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4246" t="n">
+        <v>232175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-20T05:30:48+00:00</t>
+          <t>2026-10-21T05:31:37+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4243</v>
+        <v>4244</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-20T05:30:48+00:00</t>
+          <t>2026-10-21T05:31:37+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4243</v>
+        <v>4244</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-20T05:30:48+00:00</t>
+          <t>2026-10-21T05:31:37+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4245</v>
+        <v>4246</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4244"/>
+  <dimension ref="A1:B4245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34527,6 +34527,14 @@
       </c>
       <c r="B4244" t="n">
         <v>14496</v>
+      </c>
+    </row>
+    <row r="4245">
+      <c r="A4245" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4245" t="n">
+        <v>14540</v>
       </c>
     </row>
   </sheetData>
@@ -34540,7 +34548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4244"/>
+  <dimension ref="A1:B4245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68497,6 +68505,14 @@
       </c>
       <c r="B4244" t="n">
         <v>14378</v>
+      </c>
+    </row>
+    <row r="4245">
+      <c r="A4245" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4245" t="n">
+        <v>14357</v>
       </c>
     </row>
   </sheetData>
@@ -68510,7 +68526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4246"/>
+  <dimension ref="A1:B4247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102485,6 +102501,14 @@
         <v>232175</v>
       </c>
     </row>
+    <row r="4247">
+      <c r="A4247" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4247" t="n">
+        <v>233800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-21T05:31:37+00:00</t>
+          <t>2026-10-22T05:35:42+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4244</v>
+        <v>4245</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-21T05:31:37+00:00</t>
+          <t>2026-10-22T05:35:42+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4244</v>
+        <v>4245</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-21T05:31:37+00:00</t>
+          <t>2026-10-22T05:35:42+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4246</v>
+        <v>4247</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4245"/>
+  <dimension ref="A1:B4246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34535,6 +34535,14 @@
       </c>
       <c r="B4245" t="n">
         <v>14540</v>
+      </c>
+    </row>
+    <row r="4246">
+      <c r="A4246" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4246" t="n">
+        <v>14441</v>
       </c>
     </row>
   </sheetData>
@@ -34548,7 +34556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4245"/>
+  <dimension ref="A1:B4246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68513,6 +68521,14 @@
       </c>
       <c r="B4245" t="n">
         <v>14357</v>
+      </c>
+    </row>
+    <row r="4246">
+      <c r="A4246" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4246" t="n">
+        <v>14315</v>
       </c>
     </row>
   </sheetData>
@@ -68526,7 +68542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4247"/>
+  <dimension ref="A1:B4248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102509,6 +102525,14 @@
         <v>233800</v>
       </c>
     </row>
+    <row r="4248">
+      <c r="A4248" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4248" t="n">
+        <v>245275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-22T05:35:42+00:00</t>
+          <t>2026-10-23T05:33:36+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4245</v>
+        <v>4246</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-22T05:35:42+00:00</t>
+          <t>2026-10-23T05:33:36+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4245</v>
+        <v>4246</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-22T05:35:42+00:00</t>
+          <t>2026-10-23T05:33:36+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4247</v>
+        <v>4248</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4246"/>
+  <dimension ref="A1:B4247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34543,6 +34543,14 @@
       </c>
       <c r="B4246" t="n">
         <v>14441</v>
+      </c>
+    </row>
+    <row r="4247">
+      <c r="A4247" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4247" t="n">
+        <v>14215</v>
       </c>
     </row>
   </sheetData>
@@ -34556,7 +34564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4246"/>
+  <dimension ref="A1:B4247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68529,6 +68537,14 @@
       </c>
       <c r="B4246" t="n">
         <v>14315</v>
+      </c>
+    </row>
+    <row r="4247">
+      <c r="A4247" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4247" t="n">
+        <v>14096</v>
       </c>
     </row>
   </sheetData>
@@ -68542,7 +68558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4248"/>
+  <dimension ref="A1:B4249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102533,6 +102549,14 @@
         <v>245275</v>
       </c>
     </row>
+    <row r="4249">
+      <c r="A4249" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4249" t="n">
+        <v>272950</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-23T05:33:36+00:00</t>
+          <t>2026-10-26T05:34:20+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4246</v>
+        <v>4247</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-23T05:33:36+00:00</t>
+          <t>2026-10-26T05:34:20+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4246</v>
+        <v>4247</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-23T05:33:36+00:00</t>
+          <t>2026-10-26T05:34:20+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4248</v>
+        <v>4249</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4247"/>
+  <dimension ref="A1:B4248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34551,6 +34551,14 @@
       </c>
       <c r="B4247" t="n">
         <v>14215</v>
+      </c>
+    </row>
+    <row r="4248">
+      <c r="A4248" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4248" t="n">
+        <v>14415</v>
       </c>
     </row>
   </sheetData>
@@ -34564,7 +34572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4247"/>
+  <dimension ref="A1:B4248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68545,6 +68553,14 @@
       </c>
       <c r="B4247" t="n">
         <v>14096</v>
+      </c>
+    </row>
+    <row r="4248">
+      <c r="A4248" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4248" t="n">
+        <v>14270</v>
       </c>
     </row>
   </sheetData>
@@ -68558,7 +68574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4249"/>
+  <dimension ref="A1:B4250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102557,6 +102573,14 @@
         <v>272950</v>
       </c>
     </row>
+    <row r="4250">
+      <c r="A4250" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4250" t="n">
+        <v>273750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-26T05:34:20+00:00</t>
+          <t>2026-10-27T05:48:40+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4247</v>
+        <v>4248</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-26T05:34:20+00:00</t>
+          <t>2026-10-27T05:48:40+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4247</v>
+        <v>4248</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-26T05:34:20+00:00</t>
+          <t>2026-10-27T05:48:40+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4249</v>
+        <v>4250</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4248"/>
+  <dimension ref="A1:B4249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34559,6 +34559,14 @@
       </c>
       <c r="B4248" t="n">
         <v>14415</v>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4249" t="n">
+        <v>14500</v>
       </c>
     </row>
   </sheetData>
@@ -34572,7 +34580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4248"/>
+  <dimension ref="A1:B4249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68561,6 +68569,14 @@
       </c>
       <c r="B4248" t="n">
         <v>14270</v>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4249" t="n">
+        <v>14332</v>
       </c>
     </row>
   </sheetData>
@@ -68574,7 +68590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4250"/>
+  <dimension ref="A1:B4251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102581,6 +102597,14 @@
         <v>273750</v>
       </c>
     </row>
+    <row r="4251">
+      <c r="A4251" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4251" t="n">
+        <v>272975</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-27T05:48:40+00:00</t>
+          <t>2026-10-28T06:27:25+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4248</v>
+        <v>4249</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-27T05:48:40+00:00</t>
+          <t>2026-10-28T06:27:25+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4248</v>
+        <v>4249</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-27T05:48:40+00:00</t>
+          <t>2026-10-28T06:27:25+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4250</v>
+        <v>4251</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4249"/>
+  <dimension ref="A1:B4250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34567,6 +34567,14 @@
       </c>
       <c r="B4249" t="n">
         <v>14500</v>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4250" t="n">
+        <v>14625</v>
       </c>
     </row>
   </sheetData>
@@ -34580,7 +34588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4249"/>
+  <dimension ref="A1:B4250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68577,6 +68585,14 @@
       </c>
       <c r="B4249" t="n">
         <v>14332</v>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4250" t="n">
+        <v>14435</v>
       </c>
     </row>
   </sheetData>
@@ -68590,7 +68606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4251"/>
+  <dimension ref="A1:B4252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102605,6 +102621,14 @@
         <v>272975</v>
       </c>
     </row>
+    <row r="4252">
+      <c r="A4252" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4252" t="n">
+        <v>272725</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-28T06:27:25+00:00</t>
+          <t>2026-10-29T06:38:03+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4249</v>
+        <v>4250</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-28T06:27:25+00:00</t>
+          <t>2026-10-29T06:38:03+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4249</v>
+        <v>4250</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-28T06:27:25+00:00</t>
+          <t>2026-10-29T06:38:03+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4251</v>
+        <v>4252</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4250"/>
+  <dimension ref="A1:B4251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34575,6 +34575,14 @@
       </c>
       <c r="B4250" t="n">
         <v>14625</v>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4251" t="n">
+        <v>14675.5</v>
       </c>
     </row>
   </sheetData>
@@ -34588,7 +34596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4250"/>
+  <dimension ref="A1:B4251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68593,6 +68601,14 @@
       </c>
       <c r="B4250" t="n">
         <v>14435</v>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4251" t="n">
+        <v>14484</v>
       </c>
     </row>
   </sheetData>
@@ -68606,7 +68622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4252"/>
+  <dimension ref="A1:B4253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102629,6 +102645,14 @@
         <v>272725</v>
       </c>
     </row>
+    <row r="4253">
+      <c r="A4253" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4253" t="n">
+        <v>271450</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cache/lme.xlsx
+++ b/data/cache/lme.xlsx
@@ -485,14 +485,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-29T06:38:03+00:00</t>
+          <t>2026-10-30T06:37:07+00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4250</v>
+        <v>4251</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-29T06:38:03+00:00</t>
+          <t>2026-10-30T06:37:07+00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4250</v>
+        <v>4251</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,14 +543,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:38:03+00:00</t>
+          <t>2026-10-30T06:37:07+00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4252</v>
+        <v>4253</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4251"/>
+  <dimension ref="A1:B4252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34583,6 +34583,14 @@
       </c>
       <c r="B4251" t="n">
         <v>14675.5</v>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4252" t="n">
+        <v>14560</v>
       </c>
     </row>
   </sheetData>
@@ -34596,7 +34604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4251"/>
+  <dimension ref="A1:B4252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68609,6 +68617,14 @@
       </c>
       <c r="B4251" t="n">
         <v>14484</v>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4252" t="n">
+        <v>14350</v>
       </c>
     </row>
   </sheetData>
@@ -68622,7 +68638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4253"/>
+  <dimension ref="A1:B4254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102653,6 +102669,14 @@
         <v>271450</v>
       </c>
     </row>
+    <row r="4254">
+      <c r="A4254" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4254" t="n">
+        <v>272200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
